--- a/grading_results.xlsx
+++ b/grading_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\rag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4177018-00BE-4B6F-971F-58C946FA3AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88903FEF-16D5-41E5-A3EE-50BEA4CD9DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1575" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="136">
   <si>
     <t>Tên môn học</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>Nội dung bài luận</t>
-  </si>
-  <si>
-    <t>Điểm</t>
   </si>
   <si>
     <t>Điểm thực tế</t>
@@ -944,6 +941,22 @@
   </si>
   <si>
     <t>04_nhom3.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  
+ĐẠI HỌC UEH 
+TRƯỜNG KINH DOANH 
+CNTK - KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH 
+KẾT THÚC MÔN HỌC 
+THƯƠNG MẠI ĐIỆN TỬ 
+DỰ ÁN ODOO – THIẾT KẾ TRANG WEBSITE BÁN HÀNG 
+BÁN SẢN PHẨM DECOR TRANH ẢNH BẰNG ĐÈN LED, ĐÈN NEON 
+KÈM THEO THIẾT KẾ THEO YÊU CẦU 
+Giảng viên: Nguyễn Thành Huy 
+Mã lớp học phầ...</t>
+  </si>
+  <si>
+    <t>7.3</t>
   </si>
   <si>
     <t>04_nhom7.pdf</t>
@@ -982,20 +995,13 @@
 Triệu Quốc Trung 31211020698 100...</t>
   </si>
   <si>
-    <t xml:space="preserve">  
-ĐẠI HỌC UEH 
-TRƯỜNG KINH DOANH 
-CNTK - KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH 
-KẾT THÚC MÔN HỌC 
-THƯƠNG MẠI ĐIỆN TỬ 
-DỰ ÁN ODOO – THIẾT KẾ TRANG WEBSITE BÁN HÀNG 
-BÁN SẢN PHẨM DECOR TRANH ẢNH BẰNG ĐÈN LED, ĐÈN NEON 
-KÈM THEO THIẾT KẾ THEO YÊU CẦU 
-Giảng viên: Nguyễn Thành Huy 
-Mã lớp học phầ...</t>
-  </si>
-  <si>
-    <t>7.3</t>
+    <t>gemini-2.0-flash</t>
+  </si>
+  <si>
+    <t>Mô hình</t>
+  </si>
+  <si>
+    <t>Điểm RAG</t>
   </si>
 </sst>
 </file>
@@ -1338,16 +1344,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="51.5703125" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1357,1002 +1364,1179 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="E2">
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="F3">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" t="s">
+        <v>133</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="F31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F32">
         <v>8</v>
       </c>
-      <c r="E3">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="F37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F39">
+        <v>5.8</v>
+      </c>
+      <c r="G39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" t="s">
+        <v>133</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40">
+        <v>3.3</v>
+      </c>
+      <c r="G40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F41">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" t="s">
+        <v>133</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="F45">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" t="s">
+        <v>103</v>
+      </c>
+      <c r="D47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" t="s">
+        <v>104</v>
+      </c>
+      <c r="F47">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="F48">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" t="s">
+        <v>109</v>
+      </c>
+      <c r="F49">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s">
+        <v>112</v>
+      </c>
+      <c r="F50">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" t="s">
+        <v>112</v>
+      </c>
+      <c r="F51">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52" t="s">
+        <v>133</v>
+      </c>
+      <c r="E52" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E53" t="s">
+        <v>117</v>
+      </c>
+      <c r="F53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" t="s">
+        <v>121</v>
+      </c>
+      <c r="D54" t="s">
+        <v>133</v>
+      </c>
+      <c r="E54" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4">
+      <c r="F54">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" t="s">
+        <v>133</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>34</v>
+      </c>
+      <c r="B56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" t="s">
+        <v>125</v>
+      </c>
+      <c r="D56" t="s">
+        <v>133</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" t="s">
+        <v>127</v>
+      </c>
+      <c r="D57" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" t="s">
+        <v>133</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58">
         <v>8</v>
       </c>
-      <c r="E5">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E30">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="E31">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="E32">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E33">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="E35">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" s="1">
-        <v>8.4</v>
-      </c>
-      <c r="E37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E38">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" t="s">
-        <v>83</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39">
-        <v>5.8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40">
-        <v>3.3</v>
-      </c>
-      <c r="F40" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E42">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B43" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" t="s">
-        <v>93</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E43">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" t="s">
-        <v>96</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E44">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" s="1">
-        <v>9.35</v>
-      </c>
-      <c r="E45">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>35</v>
-      </c>
-      <c r="B46" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" t="s">
-        <v>101</v>
-      </c>
-      <c r="D46" t="s">
-        <v>102</v>
-      </c>
-      <c r="E46">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" t="s">
-        <v>103</v>
-      </c>
-      <c r="C47" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" t="s">
-        <v>105</v>
-      </c>
-      <c r="E47">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="E48">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" t="s">
-        <v>109</v>
-      </c>
-      <c r="D49" t="s">
-        <v>110</v>
-      </c>
-      <c r="E49">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>35</v>
-      </c>
-      <c r="B51" t="s">
-        <v>114</v>
-      </c>
-      <c r="C51" t="s">
-        <v>115</v>
-      </c>
-      <c r="D51" t="s">
-        <v>113</v>
-      </c>
-      <c r="E51">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>35</v>
-      </c>
-      <c r="B52" t="s">
-        <v>116</v>
-      </c>
-      <c r="C52" t="s">
-        <v>117</v>
-      </c>
-      <c r="D52" t="s">
-        <v>118</v>
-      </c>
-      <c r="E52">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>35</v>
-      </c>
-      <c r="B53" t="s">
-        <v>119</v>
-      </c>
-      <c r="C53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D53" t="s">
-        <v>118</v>
-      </c>
-      <c r="E53">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>35</v>
-      </c>
-      <c r="B54" t="s">
-        <v>121</v>
-      </c>
-      <c r="C54" t="s">
-        <v>122</v>
-      </c>
-      <c r="D54" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" t="s">
-        <v>124</v>
-      </c>
-      <c r="D55" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>35</v>
-      </c>
-      <c r="B56" t="s">
-        <v>125</v>
-      </c>
-      <c r="C56" t="s">
-        <v>126</v>
-      </c>
-      <c r="D56" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>35</v>
-      </c>
-      <c r="B57" t="s">
-        <v>127</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="B59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59" t="s">
         <v>132</v>
       </c>
-      <c r="D57" t="s">
-        <v>133</v>
-      </c>
-      <c r="E57">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>35</v>
-      </c>
-      <c r="B58" t="s">
-        <v>128</v>
-      </c>
-      <c r="C58" t="s">
-        <v>129</v>
-      </c>
-      <c r="D58" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>35</v>
-      </c>
-      <c r="B59" t="s">
-        <v>130</v>
-      </c>
-      <c r="C59" t="s">
-        <v>131</v>
-      </c>
       <c r="D59" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59">
+        <v>133</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59">
         <v>7.5</v>
       </c>
     </row>
